--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488048_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488048_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.5032</v>
+        <v>2.4751</v>
       </c>
       <c r="E2" t="n">
         <v>1.3676</v>
       </c>
       <c r="F2" t="n">
-        <v>1.1356</v>
+        <v>1.1075</v>
       </c>
       <c r="G2" t="n">
         <v>3.0881</v>
@@ -610,13 +610,13 @@
         <v>0.7929</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.8447</v>
+        <v>-0.8728</v>
       </c>
       <c r="T2" t="n">
         <v>-0.5505</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2942</v>
+        <v>-0.3222</v>
       </c>
       <c r="V2" t="n">
         <v>-0.5331</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3223</v>
+        <v>-0.0643</v>
       </c>
       <c r="E4" t="n">
-        <v>1.3982</v>
+        <v>0.787</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.0759</v>
+        <v>-0.8512</v>
       </c>
       <c r="G4" t="n">
         <v>-0.1232</v>
@@ -766,13 +766,13 @@
         <v>0.9911</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3494</v>
+        <v>-0.736</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4847</v>
+        <v>-0.1265</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.8341</v>
+        <v>-0.6095</v>
       </c>
       <c r="V4" t="n">
         <v>-0.1962</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. STACHOVSKIJ</t>
+          <t>V. CHERNODOLIA SANZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.4494</v>
+        <v>-0.9552</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5185999999999999</v>
+        <v>0.1786</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.968</v>
+        <v>-1.1338</v>
       </c>
       <c r="G5" t="n">
-        <v>2.0655</v>
+        <v>-1.2333</v>
       </c>
       <c r="H5" t="n">
-        <v>1.6964</v>
+        <v>1.0128</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3691</v>
+        <v>-2.2461</v>
       </c>
       <c r="J5" t="n">
-        <v>2.576</v>
+        <v>0.9503</v>
       </c>
       <c r="K5" t="n">
-        <v>2.4957</v>
+        <v>1.7422</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0804</v>
+        <v>-0.7919</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.5105</v>
+        <v>-2.1836</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.7993</v>
+        <v>-0.7294</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2888</v>
+        <v>-1.4542</v>
       </c>
       <c r="P5" t="n">
-        <v>-2.5769</v>
+        <v>0.9911</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.9645</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3876</v>
+        <v>0.9911</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9321</v>
+        <v>-0.7131</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4333</v>
+        <v>-0.7717000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4987</v>
+        <v>0.0586</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.8701</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.4737</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.3438</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>V. CHERNODOLIA SANZ</t>
+          <t>D. STACHOVSKIJ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.9448</v>
+        <v>-1.2301</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0767</v>
+        <v>-0.234</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.0215</v>
+        <v>-0.9961</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.2333</v>
+        <v>2.0655</v>
       </c>
       <c r="H6" t="n">
-        <v>1.0128</v>
+        <v>1.6964</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.2461</v>
+        <v>0.3691</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9503</v>
+        <v>2.576</v>
       </c>
       <c r="K6" t="n">
-        <v>1.7422</v>
+        <v>2.4957</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.7919</v>
+        <v>0.0804</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.1836</v>
+        <v>-0.5105</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.7294</v>
+        <v>-0.7993</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.4542</v>
+        <v>0.2888</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9911</v>
+        <v>-2.5769</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-3.9645</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9911</v>
+        <v>1.3876</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.7026</v>
+        <v>0.1514</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8736</v>
+        <v>-0.3192</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1709</v>
+        <v>0.4707</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.8701</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.4737</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-2.3438</v>
       </c>
     </row>
     <row r="7">
@@ -955,10 +955,10 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.0616</v>
+        <v>-1.9597</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.9933</v>
+        <v>-1.8914</v>
       </c>
       <c r="F7" t="n">
         <v>-0.0684</v>
@@ -1000,10 +1000,10 @@
         <v>0.1982</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1248</v>
+        <v>-0.0229</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1248</v>
+        <v>-0.0229</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.6732</v>
+        <v>-2.2625</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.3353</v>
+        <v>-2.2334</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3379</v>
+        <v>-0.0291</v>
       </c>
       <c r="G8" t="n">
         <v>-0.8396</v>
@@ -1078,13 +1078,13 @@
         <v>0.7929</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.3688</v>
+        <v>-0.9581</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8736</v>
+        <v>-0.7717000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4953</v>
+        <v>-0.1864</v>
       </c>
       <c r="V8" t="n">
         <v>-0.2666</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.9494</v>
+        <v>-2.361</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.6563</v>
+        <v>-1.1241</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.2931</v>
+        <v>-1.2369</v>
       </c>
       <c r="G9" t="n">
         <v>-2.0412</v>
@@ -1156,13 +1156,13 @@
         <v>1.5858</v>
       </c>
       <c r="S9" t="n">
-        <v>-2.0293</v>
+        <v>-1.4408</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.9873</v>
+        <v>-0.4551</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.0419</v>
+        <v>-0.9858</v>
       </c>
       <c r="V9" t="n">
         <v>-0.2666</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.0369</v>
+        <v>-2.8279</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.9794</v>
+        <v>-2.8546</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.0576</v>
+        <v>0.0267</v>
       </c>
       <c r="G10" t="n">
         <v>-5.0717</v>
@@ -1234,13 +1234,13 @@
         <v>2.3787</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.1464</v>
+        <v>-1.9373</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.1818</v>
+        <v>-1.057</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.9646</v>
+        <v>-0.8804</v>
       </c>
       <c r="V10" t="n">
         <v>5.9651</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. VALOR LARA</t>
+          <t>L. FURLAN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.0931</v>
+        <v>-3.116</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.9409999999999999</v>
+        <v>-2.8809</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.1521</v>
+        <v>-0.2352</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.5668</v>
+        <v>-1.1777</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.5054</v>
+        <v>-2.6334</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.0614</v>
+        <v>1.4557</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.07340000000000001</v>
+        <v>-1.8896</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.1136</v>
+        <v>-1.9699</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0402</v>
+        <v>0.0804</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.4934</v>
+        <v>0.7119</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.3918</v>
+        <v>-0.6634</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1016</v>
+        <v>1.3754</v>
       </c>
       <c r="P11" t="n">
-        <v>0.7929</v>
+        <v>-1.5858</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.1982</v>
+        <v>-2.9733</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9911</v>
+        <v>1.3876</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.1715</v>
+        <v>-1.2931</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9360000000000001</v>
+        <v>-0.4321</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2356</v>
+        <v>-0.861</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.1476</v>
+        <v>0.9405</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2666</v>
+        <v>2.4142</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.4142</v>
+        <v>-1.4737</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>L. FURLAN</t>
+          <t>A. VALOR LARA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.6026</v>
+        <v>-3.3147</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.3113</v>
+        <v>-0.573</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2913</v>
+        <v>-2.7417</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.1777</v>
+        <v>-0.5668</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.6334</v>
+        <v>-0.5054</v>
       </c>
       <c r="I12" t="n">
-        <v>1.4557</v>
+        <v>-0.0614</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.8896</v>
+        <v>-0.07340000000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.9699</v>
+        <v>-0.1136</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0804</v>
+        <v>0.0402</v>
       </c>
       <c r="M12" t="n">
-        <v>0.7119</v>
+        <v>-0.4934</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.6634</v>
+        <v>-0.3918</v>
       </c>
       <c r="O12" t="n">
-        <v>1.3754</v>
+        <v>-0.1016</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.5858</v>
+        <v>0.7929</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.9733</v>
+        <v>-0.1982</v>
       </c>
       <c r="R12" t="n">
-        <v>1.3876</v>
+        <v>0.9911</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.7797</v>
+        <v>-1.3932</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8625</v>
+        <v>-0.5679999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.9171</v>
+        <v>-0.8252</v>
       </c>
       <c r="V12" t="n">
-        <v>0.9405</v>
+        <v>-2.1476</v>
       </c>
       <c r="W12" t="n">
-        <v>2.4142</v>
+        <v>0.2666</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.4737</v>
+        <v>-2.4142</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.0454</v>
+        <v>-4.7907</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.9716</v>
+        <v>-1.7449</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.0739</v>
+        <v>-3.0458</v>
       </c>
       <c r="G13" t="n">
         <v>-1.5628</v>
@@ -1468,13 +1468,13 @@
         <v>0.3964</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.4915</v>
+        <v>-0.2367</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4368</v>
+        <v>-0.2101</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0547</v>
+        <v>-0.0266</v>
       </c>
       <c r="V13" t="n">
         <v>-1.2071</v>
@@ -1501,16 +1501,16 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-19.5202</v>
+        <v>-18.8963</v>
       </c>
       <c r="E14" t="n">
-        <v>-10.3164</v>
+        <v>-9.692400000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>-9.2041</v>
+        <v>-9.203999999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>-6.631099999999999</v>
+        <v>-6.6311</v>
       </c>
       <c r="H14" t="n">
         <v>-5.4722</v>
@@ -1519,13 +1519,13 @@
         <v>-1.1586</v>
       </c>
       <c r="J14" t="n">
-        <v>0.7272999999999997</v>
+        <v>0.7272999999999996</v>
       </c>
       <c r="K14" t="n">
         <v>1.4919</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.7646000000000002</v>
+        <v>-0.7645999999999999</v>
       </c>
       <c r="M14" t="n">
         <v>-7.3582</v>
@@ -1534,7 +1534,7 @@
         <v>-6.9641</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.394</v>
+        <v>-0.3939999999999998</v>
       </c>
       <c r="P14" t="n">
         <v>-3.9644</v>
@@ -1546,13 +1546,13 @@
         <v>11.8934</v>
       </c>
       <c r="S14" t="n">
-        <v>-10.0766</v>
+        <v>-9.4526</v>
       </c>
       <c r="T14" t="n">
-        <v>-5.9089</v>
+        <v>-5.2848</v>
       </c>
       <c r="U14" t="n">
-        <v>-4.1679</v>
+        <v>-4.1678</v>
       </c>
       <c r="V14" t="n">
         <v>1.151699999999999</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>8.6365</v>
+        <v>8.119300000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>5.0143</v>
+        <v>4.8106</v>
       </c>
       <c r="F15" t="n">
-        <v>3.6222</v>
+        <v>3.3088</v>
       </c>
       <c r="G15" t="n">
         <v>5.8527</v>
@@ -1624,13 +1624,13 @@
         <v>2.3787</v>
       </c>
       <c r="S15" t="n">
-        <v>2.2664</v>
+        <v>1.7492</v>
       </c>
       <c r="T15" t="n">
-        <v>0.727</v>
+        <v>0.5233</v>
       </c>
       <c r="U15" t="n">
-        <v>1.5393</v>
+        <v>1.2259</v>
       </c>
       <c r="V15" t="n">
         <v>-0.8701</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.2708</v>
+        <v>6.6813</v>
       </c>
       <c r="E16" t="n">
-        <v>2.1098</v>
+        <v>2.8229</v>
       </c>
       <c r="F16" t="n">
-        <v>3.161</v>
+        <v>3.8584</v>
       </c>
       <c r="G16" t="n">
         <v>2.7551</v>
@@ -1702,13 +1702,13 @@
         <v>2.7751</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.5505</v>
+        <v>0.8599</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6202</v>
+        <v>0.0929</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0696</v>
+        <v>0.767</v>
       </c>
       <c r="V16" t="n">
         <v>2.2734</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>L. SIGISMONTI RODRÍGUEZ</t>
+          <t>P. AVALOS ORTIZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.5107</v>
+        <v>1.612</v>
       </c>
       <c r="E18" t="n">
-        <v>1.5107</v>
+        <v>-2.5123</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>4.1244</v>
       </c>
       <c r="G18" t="n">
-        <v>1.5107</v>
+        <v>-2.4819</v>
       </c>
       <c r="H18" t="n">
-        <v>0.908</v>
+        <v>-0.3795</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6027</v>
+        <v>-2.1025</v>
       </c>
       <c r="J18" t="n">
-        <v>1.5107</v>
+        <v>-3.7257</v>
       </c>
       <c r="K18" t="n">
-        <v>0.908</v>
+        <v>-1.2101</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6027</v>
+        <v>-2.5156</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>1.2438</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>0.8307</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>0.4132</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>0.7929</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.784</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>1.4904</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>0.3939</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.0965</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.8107</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.8107</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. MELERO ZURITA</t>
+          <t>L. SIGISMONTI RODRÍGUEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.3192</v>
+        <v>1.5107</v>
       </c>
       <c r="E19" t="n">
-        <v>1.8179</v>
+        <v>1.5107</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.4987</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1984</v>
+        <v>1.5107</v>
       </c>
       <c r="H19" t="n">
-        <v>0.032</v>
+        <v>0.908</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1664</v>
+        <v>0.6027</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5106000000000001</v>
+        <v>1.5107</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3499</v>
+        <v>0.908</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1607</v>
+        <v>0.6027</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.3123</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.318</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>0.0057</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9822</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9911</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>1.8454</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>1.5492</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2962</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.7403</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.4737</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.175</v>
+        <v>0.9066</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.3504</v>
+        <v>-2.0635</v>
       </c>
       <c r="F21" t="n">
-        <v>2.5255</v>
+        <v>2.9701</v>
       </c>
       <c r="G21" t="n">
         <v>-1.5089</v>
@@ -2092,13 +2092,13 @@
         <v>1.784</v>
       </c>
       <c r="S21" t="n">
-        <v>1.891</v>
+        <v>1.6226</v>
       </c>
       <c r="T21" t="n">
-        <v>1.854</v>
+        <v>1.1409</v>
       </c>
       <c r="U21" t="n">
-        <v>0.037</v>
+        <v>0.4817</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>P. AVALOS ORTIZ</t>
+          <t>D. MELERO ZURITA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.6227</v>
+        <v>0.599</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.2254</v>
+        <v>0.9011</v>
       </c>
       <c r="F22" t="n">
-        <v>3.8481</v>
+        <v>-0.3021</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.4819</v>
+        <v>0.1984</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.3795</v>
+        <v>0.032</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.1025</v>
+        <v>0.1664</v>
       </c>
       <c r="J22" t="n">
-        <v>-3.7257</v>
+        <v>0.5106000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.2101</v>
+        <v>0.3499</v>
       </c>
       <c r="L22" t="n">
-        <v>-2.5156</v>
+        <v>0.1607</v>
       </c>
       <c r="M22" t="n">
-        <v>1.2438</v>
+        <v>-0.3123</v>
       </c>
       <c r="N22" t="n">
-        <v>0.8307</v>
+        <v>-0.318</v>
       </c>
       <c r="O22" t="n">
-        <v>0.4132</v>
+        <v>0.0057</v>
       </c>
       <c r="P22" t="n">
-        <v>0.7929</v>
+        <v>-0.9911</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9911</v>
+        <v>-1.9822</v>
       </c>
       <c r="R22" t="n">
-        <v>1.784</v>
+        <v>0.9911</v>
       </c>
       <c r="S22" t="n">
-        <v>0.5011</v>
+        <v>1.1251</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3192</v>
+        <v>0.6324</v>
       </c>
       <c r="U22" t="n">
-        <v>0.8203</v>
+        <v>0.4927</v>
       </c>
       <c r="V22" t="n">
-        <v>1.8107</v>
+        <v>0.2666</v>
       </c>
       <c r="W22" t="n">
-        <v>1.8107</v>
+        <v>1.7403</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.4737</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. CEBOLLA HERRERA</t>
+          <t>M. BOTAS FERNANDEZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.07829999999999999</v>
+        <v>-0.1158</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.7033</v>
+        <v>0.7065</v>
       </c>
       <c r="F23" t="n">
-        <v>0.625</v>
+        <v>-0.8223</v>
       </c>
       <c r="G23" t="n">
-        <v>-4.5978</v>
+        <v>0.1509</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.7737000000000001</v>
+        <v>-0.7387</v>
       </c>
       <c r="I23" t="n">
-        <v>-3.8241</v>
+        <v>0.8895999999999999</v>
       </c>
       <c r="J23" t="n">
-        <v>-3.4142</v>
+        <v>1.3462</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0138</v>
+        <v>0.0605</v>
       </c>
       <c r="L23" t="n">
-        <v>-3.428</v>
+        <v>1.2857</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.1836</v>
+        <v>-1.1953</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.7875</v>
+        <v>-0.7993</v>
       </c>
       <c r="O23" t="n">
         <v>-0.3961</v>
       </c>
       <c r="P23" t="n">
-        <v>1.784</v>
+        <v>-1.784</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-1.9822</v>
       </c>
       <c r="R23" t="n">
-        <v>1.784</v>
+        <v>0.1982</v>
       </c>
       <c r="S23" t="n">
-        <v>1.2618</v>
+        <v>0.3102</v>
       </c>
       <c r="T23" t="n">
-        <v>1.2373</v>
+        <v>-0.1312</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0245</v>
+        <v>0.4413</v>
       </c>
       <c r="V23" t="n">
-        <v>1.4737</v>
+        <v>1.2071</v>
       </c>
       <c r="W23" t="n">
         <v>1.4737</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>M. BOTAS FERNANDEZ</t>
+          <t>J. CEBOLLA HERRERA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3934</v>
+        <v>-0.2893</v>
       </c>
       <c r="E24" t="n">
-        <v>0.4009</v>
+        <v>-1.1108</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.7943</v>
+        <v>0.8215</v>
       </c>
       <c r="G24" t="n">
-        <v>0.1509</v>
+        <v>-4.5978</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.7387</v>
+        <v>-0.7737000000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>0.8895999999999999</v>
+        <v>-3.8241</v>
       </c>
       <c r="J24" t="n">
-        <v>1.3462</v>
+        <v>-3.4142</v>
       </c>
       <c r="K24" t="n">
-        <v>0.0605</v>
+        <v>0.0138</v>
       </c>
       <c r="L24" t="n">
-        <v>1.2857</v>
+        <v>-3.428</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.1953</v>
+        <v>-1.1836</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.7993</v>
+        <v>-0.7875</v>
       </c>
       <c r="O24" t="n">
         <v>-0.3961</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.784</v>
+        <v>1.784</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.9822</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0.1982</v>
+        <v>1.784</v>
       </c>
       <c r="S24" t="n">
-        <v>0.0326</v>
+        <v>1.0508</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4368</v>
+        <v>0.8298</v>
       </c>
       <c r="U24" t="n">
-        <v>0.4694</v>
+        <v>0.2211</v>
       </c>
       <c r="V24" t="n">
-        <v>1.2071</v>
+        <v>1.4737</v>
       </c>
       <c r="W24" t="n">
         <v>1.4737</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.2666</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.7638</v>
+        <v>-0.9401</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9053</v>
+        <v>1.2109</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.6691</v>
+        <v>-2.151</v>
       </c>
       <c r="G25" t="n">
         <v>0.7697000000000001</v>
@@ -2404,13 +2404,13 @@
         <v>1.3876</v>
       </c>
       <c r="S25" t="n">
-        <v>1.6914</v>
+        <v>1.5151</v>
       </c>
       <c r="T25" t="n">
-        <v>0.2865</v>
+        <v>0.5921</v>
       </c>
       <c r="U25" t="n">
-        <v>1.4049</v>
+        <v>0.923</v>
       </c>
       <c r="V25" t="n">
         <v>-3.6213</v>
@@ -2425,7 +2425,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>J. VALEIRAS CREUS</t>
+          <t>R. REVELLES DIAZ</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,73 +2437,73 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-1.2779</v>
+        <v>-1.2583</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.0852</v>
+        <v>-0.1161</v>
       </c>
       <c r="F26" t="n">
-        <v>0.8073</v>
+        <v>-1.1422</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.4556</v>
+        <v>-0.6915</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.6565</v>
+        <v>-0.967</v>
       </c>
       <c r="I26" t="n">
-        <v>0.2009</v>
+        <v>0.2755</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.7469</v>
+        <v>-0.3657</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.2687</v>
+        <v>-0.3696</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.4782</v>
+        <v>0.0039</v>
       </c>
       <c r="M26" t="n">
-        <v>0.2913</v>
+        <v>-0.3258</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.3879</v>
+        <v>-0.5975</v>
       </c>
       <c r="O26" t="n">
-        <v>0.6791</v>
+        <v>0.2717</v>
       </c>
       <c r="P26" t="n">
-        <v>0.5947</v>
+        <v>0.1982</v>
       </c>
       <c r="Q26" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R26" t="n">
-        <v>1.5858</v>
+        <v>1.1893</v>
       </c>
       <c r="S26" t="n">
-        <v>1.6712</v>
+        <v>-0.1615</v>
       </c>
       <c r="T26" t="n">
-        <v>0.3268</v>
+        <v>-0.233</v>
       </c>
       <c r="U26" t="n">
-        <v>1.3444</v>
+        <v>0.07149999999999999</v>
       </c>
       <c r="V26" t="n">
-        <v>-3.0882</v>
+        <v>-0.6036</v>
       </c>
       <c r="W26" t="n">
-        <v>-0.674</v>
+        <v>1.4737</v>
       </c>
       <c r="X26" t="n">
-        <v>-2.4142</v>
+        <v>-2.0772</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>R. REVELLES DIAZ</t>
+          <t>J. VALEIRAS CREUS</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2515,67 +2515,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-1.6305</v>
+        <v>-1.7552</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.3199</v>
+        <v>-2.0852</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.3107</v>
+        <v>0.3299</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.6915</v>
+        <v>-0.4556</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.967</v>
+        <v>-0.6565</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2755</v>
+        <v>0.2009</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.3657</v>
+        <v>-0.7469</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.3696</v>
+        <v>-0.2687</v>
       </c>
       <c r="L27" t="n">
-        <v>0.0039</v>
+        <v>-0.4782</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.3258</v>
+        <v>0.2913</v>
       </c>
       <c r="N27" t="n">
-        <v>-0.5975</v>
+        <v>-0.3879</v>
       </c>
       <c r="O27" t="n">
-        <v>0.2717</v>
+        <v>0.6791</v>
       </c>
       <c r="P27" t="n">
-        <v>0.1982</v>
+        <v>0.5947</v>
       </c>
       <c r="Q27" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R27" t="n">
-        <v>1.1893</v>
+        <v>1.5858</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.5337</v>
+        <v>1.1939</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.4368</v>
+        <v>0.3268</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.0969</v>
+        <v>0.8671</v>
       </c>
       <c r="V27" t="n">
-        <v>-0.6036</v>
+        <v>-3.0882</v>
       </c>
       <c r="W27" t="n">
-        <v>1.4737</v>
+        <v>-0.674</v>
       </c>
       <c r="X27" t="n">
-        <v>-2.0772</v>
+        <v>-2.4142</v>
       </c>
     </row>
     <row r="28">
@@ -2593,19 +2593,19 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>19.5203</v>
+        <v>20.1995</v>
       </c>
       <c r="E28" t="n">
-        <v>9.203999999999999</v>
+        <v>9.204100000000002</v>
       </c>
       <c r="F28" t="n">
-        <v>10.3163</v>
+        <v>10.9955</v>
       </c>
       <c r="G28" t="n">
         <v>6.6311</v>
       </c>
       <c r="H28" t="n">
-        <v>5.4724</v>
+        <v>5.472400000000002</v>
       </c>
       <c r="I28" t="n">
         <v>1.1586</v>
@@ -2617,10 +2617,10 @@
         <v>6.9639</v>
       </c>
       <c r="L28" t="n">
-        <v>0.3942999999999995</v>
+        <v>0.3943000000000006</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.7271999999999996</v>
+        <v>-0.7272</v>
       </c>
       <c r="N28" t="n">
         <v>-1.4919</v>
@@ -2638,13 +2638,13 @@
         <v>15.8578</v>
       </c>
       <c r="S28" t="n">
-        <v>10.0767</v>
+        <v>10.7557</v>
       </c>
       <c r="T28" t="n">
-        <v>4.167800000000002</v>
+        <v>4.167899999999999</v>
       </c>
       <c r="U28" t="n">
-        <v>5.908700000000001</v>
+        <v>6.587800000000001</v>
       </c>
       <c r="V28" t="n">
         <v>-1.1517</v>
